--- a/data/trans_dic/DCD-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/DCD-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante</t>
+          <t>Población con dolor crónico discapacitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 10,61</t>
+          <t>6,47; 10,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,26</t>
+          <t>5,27; 9,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,45; 17,78</t>
+          <t>12,33; 17,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,86; 22,0</t>
+          <t>16,06; 22,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 16,62</t>
+          <t>11,22; 16,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,46; 27,69</t>
+          <t>19,32; 27,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,76; 15,45</t>
+          <t>11,86; 15,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,85; 12,16</t>
+          <t>8,76; 12,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,32; 22,1</t>
+          <t>17,73; 22,11</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,43</t>
+          <t>5,14; 8,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 8,73</t>
+          <t>5,44; 8,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 12,69</t>
+          <t>4,28; 12,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,71; 18,65</t>
+          <t>13,94; 18,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 14,99</t>
+          <t>10,56; 14,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,85; 28,51</t>
+          <t>23,8; 28,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,0; 12,78</t>
+          <t>9,97; 12,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 11,23</t>
+          <t>8,51; 11,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 19,47</t>
+          <t>11,06; 19,61</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,35</t>
+          <t>3,85; 7,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 7,43</t>
+          <t>4,17; 7,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,55; 14,28</t>
+          <t>9,45; 14,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,95; 17,39</t>
+          <t>12,1; 17,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 13,01</t>
+          <t>8,59; 13,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,99; 27,91</t>
+          <t>10,06; 27,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,61; 11,87</t>
+          <t>8,67; 12,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 9,72</t>
+          <t>6,99; 9,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,41; 19,84</t>
+          <t>11,44; 20,07</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,17</t>
+          <t>4,96; 8,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 8,93</t>
+          <t>5,42; 9,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,15; 16,81</t>
+          <t>12,27; 16,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,41; 18,08</t>
+          <t>13,65; 18,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,39; 17,33</t>
+          <t>12,46; 17,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,31; 28,11</t>
+          <t>20,34; 28,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 13,05</t>
+          <t>10,07; 13,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,73; 12,69</t>
+          <t>9,69; 12,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,01; 22,19</t>
+          <t>17,98; 22,09</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,6</t>
+          <t>5,79; 7,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,69</t>
+          <t>5,87; 7,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,76; 13,79</t>
+          <t>9,71; 13,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,09; 17,6</t>
+          <t>15,1; 17,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,91; 14,25</t>
+          <t>12,0; 14,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,84; 26,3</t>
+          <t>19,47; 26,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,85; 12,33</t>
+          <t>10,78; 12,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,21; 10,71</t>
+          <t>9,2; 10,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,09; 19,92</t>
+          <t>15,87; 19,86</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante</t>
+          <t>Población con dolor crónico discapacitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45963; 74668</t>
+          <t>45500; 76247</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34145; 62458</t>
+          <t>35542; 61478</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79097; 112970</t>
+          <t>78355; 112483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110571; 153367</t>
+          <t>111932; 154439</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>76490; 111833</t>
+          <t>75500; 112362</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>141135; 200851</t>
+          <t>140164; 202029</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>164632; 216398</t>
+          <t>166065; 218939</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>119321; 163845</t>
+          <t>118069; 163503</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>235650; 300685</t>
+          <t>241263; 300831</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50870; 85861</t>
+          <t>52279; 84065</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55667; 89298</t>
+          <t>55608; 87387</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63123; 151332</t>
+          <t>51031; 150467</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>141564; 192532</t>
+          <t>143865; 195077</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>109490; 156372</t>
+          <t>110136; 155329</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>228613; 273343</t>
+          <t>228140; 272258</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>204999; 262057</t>
+          <t>204416; 262292</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>175432; 231906</t>
+          <t>175768; 230476</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>241254; 418962</t>
+          <t>237905; 421880</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29719; 55692</t>
+          <t>29134; 55978</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31622; 56428</t>
+          <t>31694; 58019</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67314; 100662</t>
+          <t>66615; 101017</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92848; 135186</t>
+          <t>94007; 133205</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68658; 102165</t>
+          <t>67444; 102719</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>111873; 260545</t>
+          <t>93851; 259556</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>132154; 182150</t>
+          <t>133118; 184347</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>106861; 150156</t>
+          <t>107926; 152957</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>186888; 324962</t>
+          <t>187413; 328705</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46829; 77431</t>
+          <t>47054; 78667</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51673; 83759</t>
+          <t>50775; 85287</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>112633; 155778</t>
+          <t>113698; 153623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141008; 190195</t>
+          <t>143634; 193168</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>129309; 180929</t>
+          <t>130033; 178726</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>222431; 307799</t>
+          <t>222758; 309960</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>200662; 261017</t>
+          <t>201445; 260931</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>192874; 251374</t>
+          <t>191940; 253122</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>364171; 448576</t>
+          <t>363541; 446588</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>199449; 260328</t>
+          <t>198343; 256990</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>199191; 260919</t>
+          <t>199386; 259359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>337616; 477084</t>
+          <t>336018; 476740</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>537033; 626371</t>
+          <t>537418; 624984</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>422039; 505227</t>
+          <t>425440; 510224</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>736624; 976182</t>
+          <t>722617; 975036</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>757863; 861259</t>
+          <t>753113; 862980</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>639330; 743382</t>
+          <t>638683; 741169</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1154101; 1428993</t>
+          <t>1138230; 1424504</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DCD-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/DCD-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 10,84</t>
+          <t>6,27; 10,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,11</t>
+          <t>5,11; 9,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,33; 17,7</t>
+          <t>12,21; 17,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,06; 22,16</t>
+          <t>15,82; 21,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 16,7</t>
+          <t>11,07; 16,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,32; 27,85</t>
+          <t>24,02; 29,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 15,63</t>
+          <t>11,95; 15,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,76; 12,13</t>
+          <t>8,84; 12,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,73; 22,11</t>
+          <t>18,98; 22,59</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,26</t>
+          <t>4,99; 8,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 8,55</t>
+          <t>5,42; 8,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 12,61</t>
+          <t>9,6; 13,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,94; 18,9</t>
+          <t>13,71; 18,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 14,89</t>
+          <t>10,61; 14,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,8; 28,4</t>
+          <t>23,59; 28,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,97; 12,79</t>
+          <t>10,1; 12,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 11,16</t>
+          <t>8,42; 11,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,06; 19,61</t>
+          <t>17,26; 20,37</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,39</t>
+          <t>3,96; 7,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,64</t>
+          <t>4,16; 7,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,45; 14,34</t>
+          <t>9,65; 14,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,1; 17,14</t>
+          <t>12,43; 17,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,59; 13,09</t>
+          <t>8,8; 13,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 27,81</t>
+          <t>24,73; 30,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,01</t>
+          <t>8,57; 11,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 9,9</t>
+          <t>6,84; 9,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,44; 20,07</t>
+          <t>17,89; 21,62</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,3</t>
+          <t>5,03; 8,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 9,1</t>
+          <t>5,44; 9,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,27; 16,58</t>
+          <t>12,03; 16,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,65; 18,36</t>
+          <t>13,84; 18,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,46; 17,12</t>
+          <t>12,36; 17,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,34; 28,31</t>
+          <t>24,81; 29,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 13,05</t>
+          <t>9,96; 12,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 12,78</t>
+          <t>9,75; 12,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,98; 22,09</t>
+          <t>19,37; 22,59</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,5</t>
+          <t>5,78; 7,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,64</t>
+          <t>5,94; 7,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,78</t>
+          <t>11,84; 14,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,1; 17,56</t>
+          <t>15,09; 17,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,0; 14,39</t>
+          <t>11,92; 14,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,47; 26,27</t>
+          <t>25,49; 28,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,78; 12,35</t>
+          <t>10,85; 12,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,2; 10,68</t>
+          <t>9,25; 10,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,87; 19,86</t>
+          <t>19,06; 20,87</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95102</t>
+          <t>101063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>179427</t>
+          <t>193411</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>274529</t>
+          <t>294474</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45500; 76247</t>
+          <t>44073; 76054</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35542; 61478</t>
+          <t>34508; 60746</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78355; 112483</t>
+          <t>84314; 120945</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111932; 154439</t>
+          <t>110277; 151727</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>75500; 112362</t>
+          <t>74508; 112408</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>140164; 202029</t>
+          <t>176361; 214774</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>166065; 218939</t>
+          <t>167376; 217355</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>118069; 163503</t>
+          <t>119164; 163647</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>241263; 300831</t>
+          <t>270489; 321824</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112307</t>
+          <t>119330</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>250806</t>
+          <t>277663</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>363113</t>
+          <t>396994</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52279; 84065</t>
+          <t>50834; 85813</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55608; 87387</t>
+          <t>55462; 87940</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51031; 150467</t>
+          <t>100679; 142307</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>143865; 195077</t>
+          <t>141534; 190735</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>110136; 155329</t>
+          <t>110701; 154028</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>228140; 272258</t>
+          <t>252738; 303874</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>204416; 262292</t>
+          <t>207001; 266232</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>175768; 230476</t>
+          <t>173900; 232167</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>237905; 421880</t>
+          <t>365889; 431962</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83173</t>
+          <t>95024</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193052</t>
+          <t>225050</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>276224</t>
+          <t>320074</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29134; 55978</t>
+          <t>29973; 57970</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31694; 58019</t>
+          <t>31563; 58261</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66615; 101017</t>
+          <t>77507; 114107</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94007; 133205</t>
+          <t>96627; 137367</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67444; 102719</t>
+          <t>69059; 105106</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93851; 259556</t>
+          <t>200902; 248956</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>133118; 184347</t>
+          <t>131571; 181000</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>107926; 152957</t>
+          <t>105686; 150490</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>187413; 328705</t>
+          <t>288985; 349270</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133463</t>
+          <t>139493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>276668</t>
+          <t>301786</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>410131</t>
+          <t>441279</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47054; 78667</t>
+          <t>47702; 78584</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50775; 85287</t>
+          <t>51008; 84421</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>113698; 153623</t>
+          <t>119081; 161815</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>143634; 193168</t>
+          <t>145551; 192475</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>130033; 178726</t>
+          <t>128960; 178271</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>222758; 309960</t>
+          <t>277593; 329419</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>201445; 260931</t>
+          <t>199094; 257684</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>191940; 253122</t>
+          <t>193116; 249781</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>363541; 446588</t>
+          <t>408434; 476477</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>424045</t>
+          <t>454911</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>899952</t>
+          <t>997910</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1323997</t>
+          <t>1452821</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>198343; 256990</t>
+          <t>198146; 256925</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>199386; 259359</t>
+          <t>201723; 258952</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>336018; 476740</t>
+          <t>418162; 503157</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>537418; 624984</t>
+          <t>536814; 626754</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>425440; 510224</t>
+          <t>422673; 503963</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>722617; 975036</t>
+          <t>952398; 1048222</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>753113; 862980</t>
+          <t>757979; 871047</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>638683; 741169</t>
+          <t>642058; 743100</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1138230; 1424504</t>
+          <t>1385950; 1517258</t>
         </is>
       </c>
     </row>
